--- a/output/pdf_financials_xlsx/SUR.xlsx
+++ b/output/pdf_financials_xlsx/SUR.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.295606</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.623598</v>
       </c>
     </row>
     <row r="93">
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.520232</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>3.217288</v>
+        <v>2.775411</v>
       </c>
     </row>
     <row r="119">
@@ -2810,7 +2810,11 @@
           <t>Reserves 11,12</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>3.295606</v>
       </c>
@@ -3340,7 +3344,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>-0.520232</v>
       </c>

--- a/output/pdf_financials_xlsx/SUR.xlsx
+++ b/output/pdf_financials_xlsx/SUR.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003467</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001928</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.886109</v>
+        <v>-0.889576</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.093473</v>
+        <v>-4.095401</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.811318</v>
+        <v>-0.814785</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.050685</v>
+        <v>-4.052613</v>
       </c>
     </row>
     <row r="30">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
